--- a/education_forms/043_sports_coach_interview_form--education_forms.xlsx
+++ b/education_forms/043_sports_coach_interview_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -765,8 +765,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -794,12 +794,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'High School'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -811,12 +811,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'some_college'}</t>
+          <t>some_college</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Some College'}</t>
+          <t>Some College</t>
         </is>
       </c>
     </row>
@@ -828,12 +828,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_"bachelor's"}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': "Bachelor's"}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_"master's"}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': "Master's"}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -862,12 +862,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'doctorate'}</t>
+          <t>doctorate</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Doctorate'}</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -879,12 +879,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'coaching_certification_1'}</t>
+          <t>coaching_certification_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Coaching Certification 1'}</t>
+          <t>Coaching Certification 1</t>
         </is>
       </c>
     </row>
@@ -896,12 +896,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'coaching_certification_2'}</t>
+          <t>coaching_certification_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Coaching Certification 2'}</t>
+          <t>Coaching Certification 2</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'reference_1'}</t>
+          <t>reference_1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Reference 1'}</t>
+          <t>Reference 1</t>
         </is>
       </c>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'reference_2'}</t>
+          <t>reference_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Reference 2'}</t>
+          <t>Reference 2</t>
         </is>
       </c>
     </row>
@@ -947,12 +947,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'reference_3'}</t>
+          <t>reference_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Reference 3'}</t>
+          <t>Reference 3</t>
         </is>
       </c>
     </row>
